--- a/EconAutomation/src/supporting_docs/econ_wb_templates/current_mastertemplate.xlsx
+++ b/EconAutomation/src/supporting_docs/econ_wb_templates/current_mastertemplate.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4AEC90-4C08-A54C-82A7-04D6A1556737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{765FF91D-C91B-E74A-AE6E-CE36BB29D05E}"/>
+    <workbookView xWindow="28635" yWindow="0" windowWidth="12690" windowHeight="15705" activeTab="1" xr2:uid="{765FF91D-C91B-E74A-AE6E-CE36BB29D05E}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT_OUTPUTS" sheetId="1" r:id="rId1"/>
